--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Сектор</t>
   </si>
@@ -121,6 +121,33 @@
   </si>
   <si>
     <t>ДОБЫЧА ПОЛЕЗНЫХ ИСКОПАЕМЫХ</t>
+  </si>
+  <si>
+    <t>Оптимизация извлечения полезных ископаемых</t>
+  </si>
+  <si>
+    <t>Геолого-геофизическое моделирование и прогнозирование</t>
+  </si>
+  <si>
+    <t>Оптимизация производственных процессов и режимов добычи</t>
+  </si>
+  <si>
+    <t>Повышение производительности и эффективности оборудования</t>
+  </si>
+  <si>
+    <t>Снижение ресурсоёмкости и себестоимости добычи</t>
+  </si>
+  <si>
+    <t>Управление рисками и обеспечение промышленной безопасности</t>
+  </si>
+  <si>
+    <t>Повышение качества и концентрации добываемого сырья</t>
+  </si>
+  <si>
+    <t>Оптимизация логистики и инфраструктуры добычи</t>
+  </si>
+  <si>
+    <t>Комплексное освоение месторождений и сокращение потерь</t>
   </si>
 </sst>
 </file>
@@ -145,18 +172,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -182,6 +203,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF33CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -195,15 +228,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -218,12 +251,20 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF33CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -503,7 +544,7 @@
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
     <col min="2" max="2" width="73.42578125" customWidth="1"/>
-    <col min="3" max="3" width="58.5703125" customWidth="1"/>
+    <col min="3" max="3" width="65.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -529,51 +570,80 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="C4" s="5" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="C5" s="6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="C6" s="5" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="C7" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="C8" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="C9" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C10" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>11</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -585,74 +655,74 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>21</v>
       </c>
     </row>

--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
   <si>
     <t>Сектор</t>
   </si>
@@ -148,6 +148,78 @@
   </si>
   <si>
     <t>Комплексное освоение месторождений и сокращение потерь</t>
+  </si>
+  <si>
+    <t>СЕКТОР С</t>
+  </si>
+  <si>
+    <t>ОБРАБАТЫВАЮЩИЕ ПРОИЗВОДСТВА</t>
+  </si>
+  <si>
+    <t>Повышение производительности и эффективности производственных процессов</t>
+  </si>
+  <si>
+    <t>Автоматизация и цифровизация производства</t>
+  </si>
+  <si>
+    <t>Оптимизация использования сырья, материалов и энергии</t>
+  </si>
+  <si>
+    <t>Повышение качества и снижение брака</t>
+  </si>
+  <si>
+    <t>Разработка новых продуктов, материалов и технологий</t>
+  </si>
+  <si>
+    <t>Оптимизация производственного планирования и цепочек поставок</t>
+  </si>
+  <si>
+    <t>Повышение сложности и технологичности продукции</t>
+  </si>
+  <si>
+    <t>Снижение себестоимости и повышение экономической эффективности</t>
+  </si>
+  <si>
+    <t>Адаптация продукции к требованиям рынка и расширение рынков сбыта</t>
+  </si>
+  <si>
+    <t>Надёжность, безопасность и устойчивость производства</t>
+  </si>
+  <si>
+    <t>СЕКТОР F</t>
+  </si>
+  <si>
+    <t>СТРОИТЕЛЬСТВО</t>
+  </si>
+  <si>
+    <t>Оптимизация проектирования и инженерных решений</t>
+  </si>
+  <si>
+    <t>Оптимизация строительных процессов и последовательности работ</t>
+  </si>
+  <si>
+    <t>Повышение производительности труда и техники</t>
+  </si>
+  <si>
+    <t>Управление материалами и ресурсами</t>
+  </si>
+  <si>
+    <t>Планирование сроков и управление проектами</t>
+  </si>
+  <si>
+    <t>Контроль качества и выявление дефектов</t>
+  </si>
+  <si>
+    <t>Управление рисками, безопасностью и надёжностью</t>
+  </si>
+  <si>
+    <t>Оптимизация закупок и цепочек поставок</t>
+  </si>
+  <si>
+    <t>Повышение качества и потребительской ценности объектов</t>
+  </si>
+  <si>
+    <t>Индустриализация и внедрение новых строительных технологий</t>
   </si>
 </sst>
 </file>
@@ -539,23 +611,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
-    <col min="2" max="2" width="73.42578125" customWidth="1"/>
+    <col min="2" max="2" width="62.85546875" customWidth="1"/>
     <col min="3" max="3" width="65.42578125" customWidth="1"/>
+    <col min="4" max="4" width="64.85546875" customWidth="1"/>
+    <col min="5" max="5" width="59.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,8 +645,14 @@
       <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -576,74 +662,134 @@
       <c r="C3" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
         <v>42</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">

--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
   <si>
     <t>Сектор</t>
   </si>
@@ -220,6 +220,120 @@
   </si>
   <si>
     <t>Индустриализация и внедрение новых строительных технологий</t>
+  </si>
+  <si>
+    <t>СЕКТОР G</t>
+  </si>
+  <si>
+    <t>ТОРГОВЛЯ ОПТОВАЯ И РОЗНИЧНАЯ; РЕМОНТ АВТОТРАНСПОРТНЫХ СРЕДСТВ И МОТОЦИКЛОВ</t>
+  </si>
+  <si>
+    <t>Оптимизация ассортимента и товарной структуры</t>
+  </si>
+  <si>
+    <t>Прогнозирование спроса и поведения покупателей</t>
+  </si>
+  <si>
+    <t>Оптимизация закупок и цен</t>
+  </si>
+  <si>
+    <t>Управление запасами и товарными потоками</t>
+  </si>
+  <si>
+    <t>Оптимизация логистики и цепочек поставок</t>
+  </si>
+  <si>
+    <t>Повышение эффективности продаж и взаимодействия с клиентом</t>
+  </si>
+  <si>
+    <t>Автоматизация торговых и складских операций</t>
+  </si>
+  <si>
+    <t>Повышение эффективности ремонта и технического обслуживания автомобилей и мотоциклов</t>
+  </si>
+  <si>
+    <t>Развитие дополнительных услуг и повышение потребительской ценности</t>
+  </si>
+  <si>
+    <t>СЕКТОР H</t>
+  </si>
+  <si>
+    <t>ТРАНСПОРТИРОВКА И ХРАНЕНИЕ</t>
+  </si>
+  <si>
+    <t>Оптимизация маршрутов и транспортных потоков</t>
+  </si>
+  <si>
+    <t>Оптимизация загрузки транспортных средств и инфраструктуры</t>
+  </si>
+  <si>
+    <t>Планирование и диспетчеризация перевозок</t>
+  </si>
+  <si>
+    <t>Управление запасами и складскими операциями</t>
+  </si>
+  <si>
+    <t>Прогнозирование спроса и транспортных потоков</t>
+  </si>
+  <si>
+    <t>Повышение эффективности и технической готовности транспорта</t>
+  </si>
+  <si>
+    <t>Безопасность и надёжность перевозок</t>
+  </si>
+  <si>
+    <t>ДЕЯТЕЛЬНОСТЬ В ОБЛАСТИ ИНФОРМАЦИИ И СВЯЗИ</t>
+  </si>
+  <si>
+    <t>СЕКТОР J</t>
+  </si>
+  <si>
+    <t>Разработка новых цифровых продуктов, технологий и контента</t>
+  </si>
+  <si>
+    <t>Повышение производительности и автоматизация информационных процессов</t>
+  </si>
+  <si>
+    <t>Оптимизация информационных и телекоммуникационных систем</t>
+  </si>
+  <si>
+    <t>Обработка, анализ и использование данных</t>
+  </si>
+  <si>
+    <t>Повышение качества, надёжности и безопасности цифровых продуктов и инфраструктуры</t>
+  </si>
+  <si>
+    <t>Прогнозирование спроса и поведения пользователей</t>
+  </si>
+  <si>
+    <t>Масштабирование и эффективное распространение цифровых продуктов и услуг</t>
+  </si>
+  <si>
+    <t>СЕКТОР K</t>
+  </si>
+  <si>
+    <t>ДЕЯТЕЛЬНОСТЬ ФИНАНСОВАЯ И СТРАХОВАЯ</t>
+  </si>
+  <si>
+    <t>Оценка кредитных и финансовых рисков</t>
+  </si>
+  <si>
+    <t>Оптимизация распределения капитала и инвестиций</t>
+  </si>
+  <si>
+    <t>Прогнозирование финансовых рынков и экономических показателей</t>
+  </si>
+  <si>
+    <t>Оптимизация финансовых продуктов и условий</t>
+  </si>
+  <si>
+    <t>Управление страховыми рисками и оценка вероятности страховых событий</t>
+  </si>
+  <si>
+    <t>Выявление мошенничества, аномалий и финансовых нарушений</t>
+  </si>
+  <si>
+    <t>Автоматизация и повышение производительности финансовых операций</t>
   </si>
 </sst>
 </file>
@@ -300,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -325,6 +439,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,17 +735,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
-    <col min="2" max="2" width="62.85546875" customWidth="1"/>
+    <col min="2" max="2" width="72.5703125" customWidth="1"/>
     <col min="3" max="3" width="65.42578125" customWidth="1"/>
     <col min="4" max="4" width="64.85546875" customWidth="1"/>
     <col min="5" max="5" width="59.85546875" customWidth="1"/>
+    <col min="6" max="6" width="65.7109375" customWidth="1"/>
+    <col min="7" max="7" width="62.5703125" customWidth="1"/>
+    <col min="8" max="8" width="71.85546875" customWidth="1"/>
+    <col min="9" max="9" width="73" customWidth="1"/>
+    <col min="10" max="10" width="57.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
@@ -634,8 +763,20 @@
       <c r="E1" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -651,8 +792,20 @@
       <c r="E2" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -668,8 +821,20 @@
       <c r="E3" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
@@ -682,8 +847,20 @@
       <c r="E4" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
@@ -696,8 +873,20 @@
       <c r="E5" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
@@ -710,8 +899,20 @@
       <c r="E6" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
@@ -724,8 +925,20 @@
       <c r="E7" s="6" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
@@ -738,8 +951,20 @@
       <c r="E8" s="8" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
@@ -752,8 +977,20 @@
       <c r="E9" s="6" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
@@ -766,8 +1003,11 @@
       <c r="E10" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>11</v>
       </c>
@@ -780,8 +1020,11 @@
       <c r="E11" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
         <v>42</v>
       </c>

--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -373,12 +373,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -397,7 +391,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF33CC"/>
+        <fgColor rgb="FFF15959"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF66CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,21 +434,21 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,6 +458,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF66CC"/>
+      <color rgb="FFF15959"/>
       <color rgb="FFFF33CC"/>
     </mruColors>
   </colors>
@@ -792,7 +794,7 @@
       <c r="E2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -809,106 +811,106 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>101</v>
       </c>
     </row>
@@ -916,25 +918,25 @@
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>102</v>
       </c>
     </row>
@@ -942,65 +944,65 @@
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>74</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>64</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -1008,16 +1010,16 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="11" t="s">
         <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -1025,10 +1027,10 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="12" t="s">
         <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -1044,26 +1046,26 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1076,42 +1078,42 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="11" t="s">
         <v>21</v>
       </c>
     </row>

--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
+    <sheet name="VDS factors" sheetId="1" r:id="rId1"/>
+    <sheet name="Index of potential AI impact" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
   <si>
     <t>Сектор</t>
   </si>
@@ -334,6 +335,30 @@
   </si>
   <si>
     <t>Автоматизация и повышение производительности финансовых операций</t>
+  </si>
+  <si>
+    <t>ФАКТОРЫ ВДС (Сектор А)</t>
+  </si>
+  <si>
+    <t>Significance</t>
+  </si>
+  <si>
+    <t>Capabilty</t>
+  </si>
+  <si>
+    <t>Impact (avg)</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Total =</t>
+  </si>
+  <si>
+    <t>Total(10) =</t>
+  </si>
+  <si>
+    <t>Total(8) =</t>
   </si>
 </sst>
 </file>
@@ -414,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -448,6 +473,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1121,4 +1152,400 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="75" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E2" s="13">
+        <f>B2*C2*D2</f>
+        <v>0.06</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="13">
+        <f>B3*C3*D3</f>
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E4" s="13">
+        <f t="shared" ref="E4:E9" si="0">B4*C4*D4</f>
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E5" s="13">
+        <f t="shared" si="0"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="13">
+        <f t="shared" si="0"/>
+        <v>8.0000000000000016E-2</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E7" s="13">
+        <f t="shared" si="0"/>
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="13">
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E9" s="13">
+        <f t="shared" si="0"/>
+        <v>0.03</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D11" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" s="14">
+        <f>SUM(E2:E9)</f>
+        <v>0.37349999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E13" s="13">
+        <f t="shared" ref="E13:E22" si="1">B13*C13*D13</f>
+        <v>8.4000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="13">
+        <f t="shared" si="1"/>
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E15" s="13">
+        <f t="shared" si="1"/>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E16" s="13">
+        <f t="shared" si="1"/>
+        <v>2.7999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="13">
+        <f t="shared" si="1"/>
+        <v>2.7999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="13">
+        <f t="shared" si="1"/>
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E19" s="13">
+        <f t="shared" si="1"/>
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E20" s="13">
+        <f t="shared" si="1"/>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E21" s="13">
+        <f t="shared" si="1"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E22" s="13">
+        <f t="shared" si="1"/>
+        <v>1.6000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="14">
+        <f>SUM(E13:E20)</f>
+        <v>0.43100000000000005</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D25" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E25" s="14">
+        <f>SUM(E13:E22)</f>
+        <v>0.46500000000000008</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
   <si>
     <t>Сектор</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>Total(8) =</t>
+  </si>
+  <si>
+    <t>Сектор В</t>
   </si>
 </sst>
 </file>
@@ -1156,16 +1159,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>105</v>
       </c>
@@ -1182,7 +1185,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -1199,14 +1202,33 @@
         <f>B2*C2*D2</f>
         <v>0.06</v>
       </c>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G2" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="H2" s="2">
+        <f>I2+J2</f>
+        <v>0.8</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="N2" s="2">
+        <v>0.36</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C3" s="2">
         <v>0.6</v>
@@ -1216,11 +1238,31 @@
       </c>
       <c r="E3" s="13">
         <f>B3*C3*D3</f>
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H9" si="0">I3+J3</f>
+        <v>0.8</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="N3" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="O3" s="2">
+        <f>O2*2</f>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -1234,12 +1276,32 @@
         <v>0.3</v>
       </c>
       <c r="E4" s="13">
-        <f t="shared" ref="E4:E9" si="0">B4*C4*D4</f>
+        <f>B4*C4*D4</f>
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G4" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="N4" s="2">
+        <v>0.44</v>
+      </c>
+      <c r="O4" s="2">
+        <f>O3*2</f>
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -1253,12 +1315,32 @@
         <v>0.2</v>
       </c>
       <c r="E5" s="13">
+        <f>B5*C5*D5</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="2">
         <f t="shared" si="0"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="N5" s="2">
+        <v>0.48</v>
+      </c>
+      <c r="O5" s="2">
+        <f>O4*2</f>
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -1272,12 +1354,32 @@
         <v>0.25</v>
       </c>
       <c r="E6" s="13">
+        <f>B6*C6*D6</f>
+        <v>8.0000000000000016E-2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="H6" s="2">
         <f t="shared" si="0"/>
-        <v>8.0000000000000016E-2</v>
-      </c>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="N6" s="2">
+        <v>0.52</v>
+      </c>
+      <c r="O6" s="2">
+        <f>O5*2</f>
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -1291,12 +1393,30 @@
         <v>0.2</v>
       </c>
       <c r="E7" s="13">
+        <f>B7*C7*D7</f>
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H7" s="2">
         <f t="shared" si="0"/>
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2">
+        <f>O6*2</f>
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -1310,13 +1430,31 @@
         <v>0.2</v>
       </c>
       <c r="E8" s="13">
+        <f>B8*C8*D8</f>
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="H8" s="2">
         <f t="shared" si="0"/>
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2">
+        <f>O7*2</f>
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2">
@@ -1329,24 +1467,49 @@
         <v>0.2</v>
       </c>
       <c r="E9" s="13">
+        <f>B9*C9*D9</f>
+        <v>0.03</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="H9" s="2">
         <f t="shared" si="0"/>
-        <v>0.03</v>
-      </c>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.8</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2">
+        <f>O8*2</f>
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D11" s="1" t="s">
         <v>110</v>
       </c>
       <c r="E11" s="14">
         <f>SUM(E2:E9)</f>
-        <v>0.37349999999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.36150000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>32</v>
       </c>
@@ -1360,11 +1523,11 @@
         <v>0.2</v>
       </c>
       <c r="E13" s="13">
-        <f t="shared" ref="E13:E22" si="1">B13*C13*D13</f>
+        <f>B13*C13*D13</f>
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>34</v>
       </c>
@@ -1378,11 +1541,11 @@
         <v>0.2</v>
       </c>
       <c r="E14" s="13">
-        <f t="shared" si="1"/>
+        <f>B14*C14*D14</f>
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
@@ -1396,11 +1559,11 @@
         <v>0.2</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" si="1"/>
+        <f>B15*C15*D15</f>
         <v>0.06</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>36</v>
       </c>
@@ -1408,14 +1571,14 @@
         <v>0.2</v>
       </c>
       <c r="C16" s="2">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D16" s="2">
         <v>0.2</v>
       </c>
       <c r="E16" s="13">
-        <f t="shared" si="1"/>
-        <v>2.7999999999999997E-2</v>
+        <f>B16*C16*D16</f>
+        <v>3.2000000000000008E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1426,14 +1589,14 @@
         <v>0.2</v>
       </c>
       <c r="C17" s="2">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D17" s="2">
         <v>0.2</v>
       </c>
       <c r="E17" s="13">
-        <f t="shared" si="1"/>
-        <v>2.7999999999999997E-2</v>
+        <f>B17*C17*D17</f>
+        <v>3.2000000000000008E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1450,7 +1613,7 @@
         <v>0.2</v>
       </c>
       <c r="E18" s="13">
-        <f t="shared" si="1"/>
+        <f>B18*C18*D18</f>
         <v>2.4E-2</v>
       </c>
     </row>
@@ -1468,7 +1631,7 @@
         <v>0.6</v>
       </c>
       <c r="E19" s="13">
-        <f t="shared" si="1"/>
+        <f>B19*C19*D19</f>
         <v>0.153</v>
       </c>
     </row>
@@ -1486,7 +1649,7 @@
         <v>0.2</v>
       </c>
       <c r="E20" s="13">
-        <f t="shared" si="1"/>
+        <f>B20*C20*D20</f>
         <v>0.03</v>
       </c>
     </row>
@@ -1504,7 +1667,7 @@
         <v>0.1</v>
       </c>
       <c r="E21" s="13">
-        <f t="shared" si="1"/>
+        <f>B21*C21*D21</f>
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
@@ -1522,7 +1685,7 @@
         <v>0.2</v>
       </c>
       <c r="E22" s="13">
-        <f t="shared" si="1"/>
+        <f>B22*C22*D22</f>
         <v>1.6000000000000004E-2</v>
       </c>
     </row>
@@ -1532,7 +1695,7 @@
       </c>
       <c r="E24" s="14">
         <f>SUM(E13:E20)</f>
-        <v>0.43100000000000005</v>
+        <v>0.43900000000000006</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1541,7 +1704,7 @@
       </c>
       <c r="E25" s="14">
         <f>SUM(E13:E22)</f>
-        <v>0.46500000000000008</v>
+        <v>0.47300000000000009</v>
       </c>
     </row>
   </sheetData>

--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="VDS factors" sheetId="1" r:id="rId1"/>
@@ -775,7 +775,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
-    <col min="2" max="2" width="72.5703125" customWidth="1"/>
+    <col min="2" max="2" width="71.140625" customWidth="1"/>
     <col min="3" max="3" width="65.42578125" customWidth="1"/>
     <col min="4" max="4" width="64.85546875" customWidth="1"/>
     <col min="5" max="5" width="59.85546875" customWidth="1"/>
@@ -1163,7 +1163,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" customWidth="1"/>
   </cols>
@@ -1199,29 +1199,16 @@
         <v>0.2</v>
       </c>
       <c r="E2" s="13">
-        <f>B2*C2*D2</f>
+        <f t="shared" ref="E2:E9" si="0">B2*C2*D2</f>
         <v>0.06</v>
       </c>
-      <c r="G2" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="H2" s="2">
-        <f>I2+J2</f>
-        <v>0.8</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.2</v>
-      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="N2" s="2">
-        <v>0.36</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0.08</v>
-      </c>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1237,30 +1224,16 @@
         <v>0.2</v>
       </c>
       <c r="E3" s="13">
-        <f>B3*C3*D3</f>
+        <f t="shared" si="0"/>
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="G3" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="H3" s="2">
-        <f t="shared" ref="H3:H9" si="0">I3+J3</f>
-        <v>0.8</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.2</v>
-      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="N3" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="O3" s="2">
-        <f>O2*2</f>
-        <v>0.16</v>
-      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -1276,30 +1249,16 @@
         <v>0.3</v>
       </c>
       <c r="E4" s="13">
-        <f>B4*C4*D4</f>
+        <f t="shared" si="0"/>
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="G4" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="H4" s="2">
-        <f t="shared" si="0"/>
-        <v>0.35</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0.2</v>
-      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-      <c r="N4" s="2">
-        <v>0.44</v>
-      </c>
-      <c r="O4" s="2">
-        <f>O3*2</f>
-        <v>0.32</v>
-      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -1315,30 +1274,16 @@
         <v>0.2</v>
       </c>
       <c r="E5" s="13">
-        <f>B5*C5*D5</f>
+        <f t="shared" si="0"/>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G5" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0.2</v>
-      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-      <c r="N5" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="O5" s="2">
-        <f>O4*2</f>
-        <v>0.64</v>
-      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -1354,30 +1299,16 @@
         <v>0.25</v>
       </c>
       <c r="E6" s="13">
-        <f>B6*C6*D6</f>
+        <f t="shared" si="0"/>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="G6" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="H6" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.2</v>
-      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
       <c r="K6" s="2"/>
-      <c r="N6" s="2">
-        <v>0.52</v>
-      </c>
-      <c r="O6" s="2">
-        <f>O5*2</f>
-        <v>1.28</v>
-      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1393,28 +1324,16 @@
         <v>0.2</v>
       </c>
       <c r="E7" s="13">
-        <f>B7*C7*D7</f>
+        <f t="shared" si="0"/>
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="G7" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="H7" s="2">
-        <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.2</v>
-      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="2">
-        <f>O6*2</f>
-        <v>2.56</v>
-      </c>
+      <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1430,28 +1349,16 @@
         <v>0.2</v>
       </c>
       <c r="E8" s="13">
-        <f>B8*C8*D8</f>
+        <f t="shared" si="0"/>
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="G8" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="H8" s="2">
-        <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0.2</v>
-      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="2">
-        <f>O7*2</f>
-        <v>5.12</v>
-      </c>
+      <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1467,28 +1374,16 @@
         <v>0.2</v>
       </c>
       <c r="E9" s="13">
-        <f>B9*C9*D9</f>
+        <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
-      <c r="G9" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="H9" s="2">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0.2</v>
-      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="2">
-        <f>O8*2</f>
-        <v>10.24</v>
-      </c>
+      <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L10" s="2"/>
@@ -1523,7 +1418,7 @@
         <v>0.2</v>
       </c>
       <c r="E13" s="13">
-        <f>B13*C13*D13</f>
+        <f t="shared" ref="E13:E22" si="1">B13*C13*D13</f>
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
@@ -1541,7 +1436,7 @@
         <v>0.2</v>
       </c>
       <c r="E14" s="13">
-        <f>B14*C14*D14</f>
+        <f t="shared" si="1"/>
         <v>2.4E-2</v>
       </c>
     </row>
@@ -1559,7 +1454,7 @@
         <v>0.2</v>
       </c>
       <c r="E15" s="13">
-        <f>B15*C15*D15</f>
+        <f t="shared" si="1"/>
         <v>0.06</v>
       </c>
     </row>
@@ -1577,7 +1472,7 @@
         <v>0.2</v>
       </c>
       <c r="E16" s="13">
-        <f>B16*C16*D16</f>
+        <f t="shared" si="1"/>
         <v>3.2000000000000008E-2</v>
       </c>
     </row>
@@ -1595,7 +1490,7 @@
         <v>0.2</v>
       </c>
       <c r="E17" s="13">
-        <f>B17*C17*D17</f>
+        <f t="shared" si="1"/>
         <v>3.2000000000000008E-2</v>
       </c>
     </row>
@@ -1613,7 +1508,7 @@
         <v>0.2</v>
       </c>
       <c r="E18" s="13">
-        <f>B18*C18*D18</f>
+        <f t="shared" si="1"/>
         <v>2.4E-2</v>
       </c>
     </row>
@@ -1631,7 +1526,7 @@
         <v>0.6</v>
       </c>
       <c r="E19" s="13">
-        <f>B19*C19*D19</f>
+        <f t="shared" si="1"/>
         <v>0.153</v>
       </c>
     </row>
@@ -1649,7 +1544,7 @@
         <v>0.2</v>
       </c>
       <c r="E20" s="13">
-        <f>B20*C20*D20</f>
+        <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
     </row>
@@ -1667,7 +1562,7 @@
         <v>0.1</v>
       </c>
       <c r="E21" s="13">
-        <f>B21*C21*D21</f>
+        <f t="shared" si="1"/>
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
@@ -1685,7 +1580,7 @@
         <v>0.2</v>
       </c>
       <c r="E22" s="13">
-        <f>B22*C22*D22</f>
+        <f t="shared" si="1"/>
         <v>1.6000000000000004E-2</v>
       </c>
     </row>

--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="VDS factors" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="120">
   <si>
     <t>Сектор</t>
   </si>
@@ -349,26 +349,44 @@
     <t>Impact (avg)</t>
   </si>
   <si>
-    <t>Index</t>
-  </si>
-  <si>
     <t>Total =</t>
   </si>
   <si>
-    <t>Total(10) =</t>
-  </si>
-  <si>
-    <t>Total(8) =</t>
-  </si>
-  <si>
     <t>Сектор В</t>
+  </si>
+  <si>
+    <t>Index (avg)</t>
+  </si>
+  <si>
+    <t>Impact (max)</t>
+  </si>
+  <si>
+    <t>Impact (min)</t>
+  </si>
+  <si>
+    <t>Index (min)</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>avg</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>Index (max)</t>
+  </si>
+  <si>
+    <t>Сектор C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,9 +395,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -442,9 +477,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -462,7 +497,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -481,7 +516,17 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1159,13 +1204,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1179,10 +1229,22 @@
         <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>109</v>
+      <c r="F1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -1196,15 +1258,26 @@
         <v>0.6</v>
       </c>
       <c r="D2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E2" s="2">
         <v>0.2</v>
       </c>
-      <c r="E2" s="13">
-        <f t="shared" ref="E2:E9" si="0">B2*C2*D2</f>
+      <c r="F2" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G2" s="13">
+        <f>B2*C2*D2</f>
+        <v>0.03</v>
+      </c>
+      <c r="H2" s="13">
+        <f>B2*C2*E2</f>
         <v>0.06</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="I2" s="13">
+        <f>B2*C2*F2</f>
+        <v>0.09</v>
+      </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="N2" s="2"/>
@@ -1221,15 +1294,26 @@
         <v>0.6</v>
       </c>
       <c r="D3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="2">
         <v>0.2</v>
       </c>
-      <c r="E3" s="13">
-        <f t="shared" si="0"/>
+      <c r="F3" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G3" s="13">
+        <f t="shared" ref="G3:G9" si="0">B3*C3*D3</f>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="H3" s="13">
+        <f>B3*C3*E3</f>
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="I3" s="13">
+        <f t="shared" ref="I3:I9" si="1">B3*C3*F3</f>
+        <v>5.3999999999999999E-2</v>
+      </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="N3" s="2"/>
@@ -1246,15 +1330,26 @@
         <v>0.15</v>
       </c>
       <c r="D4" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="E4" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="G4" s="13">
         <f t="shared" si="0"/>
+        <v>1.3500000000000002E-2</v>
+      </c>
+      <c r="H4" s="13">
+        <f>B4*C4*E4</f>
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="I4" s="13">
+        <f t="shared" si="1"/>
+        <v>5.4000000000000006E-2</v>
+      </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="N4" s="2"/>
@@ -1271,15 +1366,26 @@
         <v>0.5</v>
       </c>
       <c r="D5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="2">
         <v>0.2</v>
       </c>
-      <c r="E5" s="13">
+      <c r="F5" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="13">
         <f t="shared" si="0"/>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="H5" s="13">
+        <f>B5*C5*E5</f>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="I5" s="13">
+        <f t="shared" si="1"/>
+        <v>3.7499999999999999E-2</v>
+      </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="N5" s="2"/>
@@ -1296,15 +1402,26 @@
         <v>0.8</v>
       </c>
       <c r="D6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="2">
         <v>0.25</v>
       </c>
-      <c r="E6" s="13">
+      <c r="F6" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="G6" s="13">
         <f t="shared" si="0"/>
+        <v>3.2000000000000008E-2</v>
+      </c>
+      <c r="H6" s="13">
+        <f>B6*C6*E6</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+      <c r="I6" s="13">
+        <f t="shared" si="1"/>
+        <v>0.12800000000000003</v>
+      </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="N6" s="2"/>
@@ -1321,15 +1438,26 @@
         <v>0.7</v>
       </c>
       <c r="D7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E7" s="2">
         <v>0.2</v>
       </c>
-      <c r="E7" s="13">
+      <c r="F7" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="13">
         <f t="shared" si="0"/>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="H7" s="13">
+        <f>B7*C7*E7</f>
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="I7" s="13">
+        <f t="shared" si="1"/>
+        <v>6.3E-2</v>
+      </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="N7" s="2"/>
@@ -1346,15 +1474,26 @@
         <v>0.4</v>
       </c>
       <c r="D8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="2">
         <v>0.2</v>
       </c>
-      <c r="E8" s="13">
+      <c r="F8" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="13">
         <f t="shared" si="0"/>
+        <v>2.4E-2</v>
+      </c>
+      <c r="H8" s="13">
+        <f>B8*C8*E8</f>
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="I8" s="13">
+        <f t="shared" si="1"/>
+        <v>7.1999999999999995E-2</v>
+      </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="N8" s="2"/>
@@ -1371,114 +1510,189 @@
         <v>0.6</v>
       </c>
       <c r="D9" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E9" s="2">
         <v>0.2</v>
       </c>
-      <c r="E9" s="13">
+      <c r="F9" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="13">
         <f t="shared" si="0"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H9" s="13">
+        <f>B9*C9*E9</f>
         <v>0.03</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="I9" s="13">
+        <f t="shared" si="1"/>
+        <v>4.4999999999999998E-2</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D11" s="1" t="s">
+      <c r="F11" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="15">
+        <f>SUM(G2:G9)</f>
+        <v>0.16599999999999998</v>
+      </c>
+      <c r="H11" s="15">
+        <f>SUM(H2:H9)</f>
+        <v>0.36150000000000004</v>
+      </c>
+      <c r="I11" s="15">
+        <f>SUM(I2:I9)</f>
+        <v>0.54350000000000009</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E11" s="14">
-        <f>SUM(E2:E9)</f>
-        <v>0.36150000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="E13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B14" s="2">
         <v>0.6</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C14" s="2">
         <v>0.7</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D14" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="2">
         <v>0.2</v>
       </c>
-      <c r="E13" s="13">
-        <f t="shared" ref="E13:E22" si="1">B13*C13*D13</f>
+      <c r="F14" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="13">
+        <f>B14*C14*D14</f>
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="H14" s="13">
+        <f>B14*C14*E14</f>
         <v>8.4000000000000005E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="I14" s="13">
+        <f>B14*C14*F14</f>
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B15" s="2">
         <v>0.4</v>
       </c>
-      <c r="C14" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="C15" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E15" s="2">
         <v>0.2</v>
       </c>
-      <c r="E14" s="13">
-        <f t="shared" si="1"/>
+      <c r="F15" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G15" s="13">
+        <f t="shared" ref="G15:G23" si="2">B15*C15*D15</f>
+        <v>1.2E-2</v>
+      </c>
+      <c r="H15" s="13">
+        <f>B15*C15*E15</f>
         <v>2.4E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="I15" s="13">
+        <f t="shared" ref="I15:I23" si="3">B15*C15*F15</f>
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B16" s="2">
         <v>0.6</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C16" s="2">
         <v>0.5</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D16" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E16" s="2">
         <v>0.2</v>
       </c>
-      <c r="E15" s="13">
-        <f t="shared" si="1"/>
+      <c r="F16" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G16" s="13">
+        <f t="shared" si="2"/>
+        <v>0.03</v>
+      </c>
+      <c r="H16" s="13">
+        <f>B16*C16*E16</f>
         <v>0.06</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="I16" s="13">
+        <f t="shared" si="3"/>
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="B16" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E16" s="13">
-        <f t="shared" si="1"/>
-        <v>3.2000000000000008E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="B17" s="2">
         <v>0.2</v>
@@ -1487,120 +1701,699 @@
         <v>0.8</v>
       </c>
       <c r="D17" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E17" s="2">
         <v>0.2</v>
       </c>
-      <c r="E17" s="13">
-        <f t="shared" si="1"/>
+      <c r="F17" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G17" s="13">
+        <f t="shared" si="2"/>
+        <v>1.6000000000000004E-2</v>
+      </c>
+      <c r="H17" s="13">
+        <f>B17*C17*E17</f>
         <v>3.2000000000000008E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I17" s="13">
+        <f t="shared" si="3"/>
+        <v>4.8000000000000008E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2">
         <v>0.2</v>
       </c>
       <c r="C18" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G18" s="13">
+        <f t="shared" si="2"/>
+        <v>1.6000000000000004E-2</v>
+      </c>
+      <c r="H18" s="13">
+        <f>B18*C18*E18</f>
+        <v>3.2000000000000008E-2</v>
+      </c>
+      <c r="I18" s="13">
+        <f t="shared" si="3"/>
+        <v>4.8000000000000008E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C19" s="2">
         <v>0.6</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D19" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E19" s="2">
         <v>0.2</v>
       </c>
-      <c r="E18" s="13">
-        <f t="shared" si="1"/>
+      <c r="F19" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G19" s="13">
+        <f t="shared" si="2"/>
+        <v>1.2E-2</v>
+      </c>
+      <c r="H19" s="13">
+        <f>B19*C19*E19</f>
         <v>2.4E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="I19" s="13">
+        <f t="shared" si="3"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="B20" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C20" s="2">
         <v>0.85</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D20" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="2">
         <v>0.6</v>
       </c>
-      <c r="E19" s="13">
-        <f t="shared" si="1"/>
+      <c r="F20" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="G20" s="13">
+        <f t="shared" si="2"/>
+        <v>7.6499999999999999E-2</v>
+      </c>
+      <c r="H20" s="13">
+        <f>B20*C20*E20</f>
         <v>0.153</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="I20" s="13">
+        <f t="shared" si="3"/>
+        <v>0.22950000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B21" s="2">
         <v>0.5</v>
       </c>
-      <c r="C20" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E20" s="13">
-        <f t="shared" si="1"/>
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="2">
-        <v>0.3</v>
-      </c>
       <c r="C21" s="2">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D21" s="2">
         <v>0.1</v>
       </c>
-      <c r="E21" s="13">
-        <f t="shared" si="1"/>
+      <c r="E21" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G21" s="13">
+        <f t="shared" si="2"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H21" s="13">
+        <f>B21*C21*E21</f>
+        <v>0.03</v>
+      </c>
+      <c r="I21" s="13">
+        <f t="shared" si="3"/>
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G22" s="13">
+        <f t="shared" si="2"/>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="H22" s="13">
+        <f>B22*C22*E22</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I22" s="13">
+        <f t="shared" si="3"/>
+        <v>3.7499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G23" s="13">
+        <f t="shared" si="2"/>
+        <v>8.0000000000000019E-3</v>
+      </c>
+      <c r="H23" s="13">
+        <f>B23*C23*E23</f>
+        <v>1.6000000000000004E-2</v>
+      </c>
+      <c r="I23" s="13">
+        <f t="shared" si="3"/>
+        <v>2.4000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D25" s="1"/>
+      <c r="F25" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="15">
+        <f>SUM(G14:G23)</f>
+        <v>0.23500000000000004</v>
+      </c>
+      <c r="H25" s="15">
+        <f>SUM(H14:H23)</f>
+        <v>0.47000000000000008</v>
+      </c>
+      <c r="I25" s="15">
+        <f>SUM(I14:I23)</f>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="17">
+        <v>0.4</v>
+      </c>
+      <c r="C29" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="D29" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="E29" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="F29" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G29" s="13">
+        <f>B29*C29*D29</f>
+        <v>2.0000000000000004E-2</v>
+      </c>
+      <c r="H29" s="13">
+        <f>B29*C29*E29</f>
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="I29" s="13">
+        <f>B29*C29*F29</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="C30" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="D30" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="E30" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="F30" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G30" s="13">
+        <f t="shared" ref="G30:G37" si="4">B30*C30*D30</f>
+        <v>1.7499999999999998E-2</v>
+      </c>
+      <c r="H30" s="13">
+        <f t="shared" ref="H30:I37" si="5">B30*C30*E30</f>
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="I30" s="13">
+        <f t="shared" ref="I30:I37" si="6">B30*C30*F30</f>
+        <v>5.2499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="C31" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="D31" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="E31" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="F31" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="G31" s="13">
+        <f t="shared" si="4"/>
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="H31" s="13">
+        <f t="shared" si="5"/>
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="I31" s="13">
+        <f t="shared" si="6"/>
+        <v>0.216</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="C32" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="D32" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="E32" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="F32" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="G32" s="13">
+        <f t="shared" si="4"/>
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="H32" s="13">
+        <f t="shared" si="5"/>
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="I32" s="13">
+        <f t="shared" si="6"/>
+        <v>0.12150000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="C33" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="D33" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="E33" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="F33" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="G33" s="13">
+        <f t="shared" si="4"/>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="H33" s="13">
+        <f t="shared" si="5"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I33" s="13">
+        <f t="shared" si="6"/>
+        <v>3.7499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="17">
+        <v>0.4</v>
+      </c>
+      <c r="C34" s="17">
+        <v>0.4</v>
+      </c>
+      <c r="D34" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="E34" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="F34" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G34" s="13">
+        <f t="shared" si="4"/>
+        <v>1.6000000000000004E-2</v>
+      </c>
+      <c r="H34" s="13">
+        <f t="shared" si="5"/>
+        <v>3.2000000000000008E-2</v>
+      </c>
+      <c r="I34" s="13">
+        <f t="shared" si="6"/>
+        <v>4.8000000000000008E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="C35" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="D35" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="E35" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="F35" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G35" s="13">
+        <f t="shared" si="4"/>
         <v>1.7999999999999999E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="2">
+      <c r="H35" s="13">
+        <f t="shared" si="5"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="I35" s="13">
+        <f t="shared" si="6"/>
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="C36" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="D36" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="E36" s="17">
         <v>0.2</v>
       </c>
-      <c r="C22" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="F36" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G36" s="13">
+        <f t="shared" si="4"/>
+        <v>1.7499999999999998E-2</v>
+      </c>
+      <c r="H36" s="13">
+        <f t="shared" si="5"/>
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="I36" s="13">
+        <f t="shared" si="6"/>
+        <v>5.2499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="17">
         <v>0.2</v>
       </c>
-      <c r="E22" s="13">
-        <f t="shared" si="1"/>
-        <v>1.6000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" s="14">
-        <f>SUM(E13:E20)</f>
-        <v>0.43900000000000006</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D25" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E25" s="14">
-        <f>SUM(E13:E22)</f>
-        <v>0.47300000000000009</v>
-      </c>
+      <c r="C37" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="D37" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="E37" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="F37" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="G37" s="13">
+        <f t="shared" si="4"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H37" s="13">
+        <f t="shared" si="5"/>
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="I37" s="13">
+        <f t="shared" si="6"/>
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="G38" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="G39" s="15">
+        <f>SUM(G28:G37)</f>
+        <v>0.245</v>
+      </c>
+      <c r="H39" s="15">
+        <f>SUM(H28:H37)</f>
+        <v>0.49</v>
+      </c>
+      <c r="I39" s="15">
+        <f>SUM(I28:I37)</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="18"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="18"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="18"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="18"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="18"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="18"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="18"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="18"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="18"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="18"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="16"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="16"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="18"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="16"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="116">
   <si>
     <t>Сектор</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Логистика</t>
   </si>
   <si>
-    <t xml:space="preserve">5-25% </t>
-  </si>
-  <si>
     <t>Управление запасами</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
     <t>Оптимизация энергопотребления</t>
   </si>
   <si>
-    <t>10-40%</t>
-  </si>
-  <si>
     <t>Распознование</t>
   </si>
   <si>
@@ -100,15 +94,9 @@
     <t>Комб. поиск материалов (соединений)</t>
   </si>
   <si>
-    <t>5-100 раз быстрее</t>
-  </si>
-  <si>
     <t>Комб. поиск лекарств</t>
   </si>
   <si>
-    <t>3-20 раз быстрее</t>
-  </si>
-  <si>
     <t>Комб. селекция (лучшие генотипы)</t>
   </si>
   <si>
@@ -343,21 +331,12 @@
     <t>Significance</t>
   </si>
   <si>
-    <t>Capabilty</t>
-  </si>
-  <si>
-    <t>Impact (avg)</t>
-  </si>
-  <si>
     <t>Total =</t>
   </si>
   <si>
     <t>Сектор В</t>
   </si>
   <si>
-    <t>Index (avg)</t>
-  </si>
-  <si>
     <t>Impact (max)</t>
   </si>
   <si>
@@ -370,9 +349,6 @@
     <t>min</t>
   </si>
   <si>
-    <t>avg</t>
-  </si>
-  <si>
     <t>max</t>
   </si>
   <si>
@@ -380,6 +356,18 @@
   </si>
   <si>
     <t>Сектор C</t>
+  </si>
+  <si>
+    <t>Capabilty (min)</t>
+  </si>
+  <si>
+    <t>Capabilty (max)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-15% </t>
+  </si>
+  <si>
+    <t>5-10%</t>
   </si>
 </sst>
 </file>
@@ -833,28 +821,28 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -865,25 +853,25 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -894,25 +882,25 @@
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -920,25 +908,25 @@
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -946,25 +934,25 @@
         <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -972,25 +960,25 @@
         <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -998,25 +986,25 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1024,25 +1012,25 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1050,25 +1038,25 @@
         <v>9</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1076,16 +1064,16 @@
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1093,27 +1081,27 @@
         <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1137,63 +1125,63 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>28</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1209,42 +1197,47 @@
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" customWidth="1"/>
     <col min="7" max="7" width="12.85546875" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="11" max="11" width="22.28515625" customWidth="1"/>
+    <col min="12" max="12" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>113</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>118</v>
+      <c r="L1" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -1252,34 +1245,37 @@
         <v>3</v>
       </c>
       <c r="B2" s="2">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C2" s="2">
-        <v>0.6</v>
+        <f>K$2</f>
+        <v>0.3</v>
       </c>
       <c r="D2" s="2">
+        <f>L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E2" s="2">
         <v>0.1</v>
       </c>
-      <c r="E2" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F2" s="2">
         <v>0.3</v>
       </c>
       <c r="G2" s="13">
-        <f>B2*C2*D2</f>
-        <v>0.03</v>
+        <f>B2*C2*E2</f>
+        <v>1.2E-2</v>
       </c>
       <c r="H2" s="13">
-        <f>B2*C2*E2</f>
-        <v>0.06</v>
-      </c>
-      <c r="I2" s="13">
-        <f>B2*C2*F2</f>
-        <v>0.09</v>
+        <f>B2*D2*F2</f>
+        <v>8.3999999999999991E-2</v>
       </c>
       <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="K2" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0.7</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
     </row>
@@ -1291,28 +1287,26 @@
         <v>0.3</v>
       </c>
       <c r="C3" s="2">
-        <v>0.6</v>
+        <f t="shared" ref="C3:C9" si="0">K$2</f>
+        <v>0.3</v>
       </c>
       <c r="D3" s="2">
+        <f t="shared" ref="D3:D9" si="1">L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E3" s="2">
         <v>0.1</v>
       </c>
-      <c r="E3" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F3" s="2">
         <v>0.3</v>
       </c>
       <c r="G3" s="13">
-        <f t="shared" ref="G3:G9" si="0">B3*C3*D3</f>
-        <v>1.7999999999999999E-2</v>
+        <f>B3*C3*E3</f>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="H3" s="13">
-        <f>B3*C3*E3</f>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="I3" s="13">
-        <f t="shared" ref="I3:I9" si="1">B3*C3*F3</f>
-        <v>5.3999999999999999E-2</v>
+        <f t="shared" ref="H3:H9" si="2">B3*D3*F3</f>
+        <v>6.3E-2</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1327,28 +1321,26 @@
         <v>0.9</v>
       </c>
       <c r="C4" s="2">
-        <v>0.15</v>
+        <f t="shared" si="0"/>
+        <v>0.3</v>
       </c>
       <c r="D4" s="2">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F4" s="2">
         <v>0.1</v>
       </c>
-      <c r="E4" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.4</v>
-      </c>
       <c r="G4" s="13">
-        <f t="shared" si="0"/>
+        <f>B4*C4*E4</f>
         <v>1.3500000000000002E-2</v>
       </c>
       <c r="H4" s="13">
-        <f>B4*C4*E4</f>
-        <v>4.0500000000000001E-2</v>
-      </c>
-      <c r="I4" s="13">
-        <f t="shared" si="1"/>
-        <v>5.4000000000000006E-2</v>
+        <f t="shared" si="2"/>
+        <v>6.3E-2</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1363,28 +1355,26 @@
         <v>0.25</v>
       </c>
       <c r="C5" s="2">
-        <v>0.5</v>
+        <f t="shared" si="0"/>
+        <v>0.3</v>
       </c>
       <c r="D5" s="2">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="E5" s="2">
         <v>0.1</v>
       </c>
-      <c r="E5" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F5" s="2">
         <v>0.3</v>
       </c>
       <c r="G5" s="13">
-        <f t="shared" si="0"/>
-        <v>1.2500000000000001E-2</v>
+        <f>B5*C5*E5</f>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="H5" s="13">
-        <f>B5*C5*E5</f>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="I5" s="13">
-        <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.2499999999999998E-2</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1399,28 +1389,26 @@
         <v>0.4</v>
       </c>
       <c r="C6" s="2">
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>0.3</v>
       </c>
       <c r="D6" s="2">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="E6" s="2">
         <v>0.1</v>
       </c>
-      <c r="E6" s="2">
-        <v>0.25</v>
-      </c>
       <c r="F6" s="2">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G6" s="13">
-        <f t="shared" si="0"/>
-        <v>3.2000000000000008E-2</v>
+        <f>B6*C6*E6</f>
+        <v>1.2E-2</v>
       </c>
       <c r="H6" s="13">
-        <f>B6*C6*E6</f>
-        <v>8.0000000000000016E-2</v>
-      </c>
-      <c r="I6" s="13">
-        <f t="shared" si="1"/>
-        <v>0.12800000000000003</v>
+        <f t="shared" si="2"/>
+        <v>8.3999999999999991E-2</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1435,27 +1423,25 @@
         <v>0.3</v>
       </c>
       <c r="C7" s="2">
-        <v>0.7</v>
+        <f t="shared" si="0"/>
+        <v>0.3</v>
       </c>
       <c r="D7" s="2">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="E7" s="2">
         <v>0.1</v>
       </c>
-      <c r="E7" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F7" s="2">
         <v>0.3</v>
       </c>
       <c r="G7" s="13">
-        <f t="shared" si="0"/>
-        <v>2.1000000000000001E-2</v>
+        <f>B7*C7*E7</f>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="H7" s="13">
-        <f>B7*C7*E7</f>
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="I7" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.3E-2</v>
       </c>
       <c r="J7" s="2"/>
@@ -1471,28 +1457,26 @@
         <v>0.6</v>
       </c>
       <c r="C8" s="2">
-        <v>0.4</v>
+        <f t="shared" si="0"/>
+        <v>0.3</v>
       </c>
       <c r="D8" s="2">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="E8" s="2">
         <v>0.1</v>
       </c>
-      <c r="E8" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F8" s="2">
         <v>0.3</v>
       </c>
       <c r="G8" s="13">
-        <f t="shared" si="0"/>
-        <v>2.4E-2</v>
+        <f>B8*C8*E8</f>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H8" s="13">
-        <f>B8*C8*E8</f>
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="I8" s="13">
-        <f t="shared" si="1"/>
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.126</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1507,28 +1491,26 @@
         <v>0.25</v>
       </c>
       <c r="C9" s="2">
-        <v>0.6</v>
+        <f t="shared" si="0"/>
+        <v>0.3</v>
       </c>
       <c r="D9" s="2">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="E9" s="2">
         <v>0.1</v>
       </c>
-      <c r="E9" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F9" s="2">
         <v>0.3</v>
       </c>
       <c r="G9" s="13">
-        <f t="shared" si="0"/>
-        <v>1.4999999999999999E-2</v>
+        <f>B9*C9*E9</f>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="H9" s="13">
-        <f>B9*C9*E9</f>
-        <v>0.03</v>
-      </c>
-      <c r="I9" s="13">
-        <f t="shared" si="1"/>
-        <v>4.4999999999999998E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.2499999999999998E-2</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1537,823 +1519,758 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G10" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F11" s="14" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G11" s="15">
         <f>SUM(G2:G9)</f>
-        <v>0.16599999999999998</v>
+        <v>8.8499999999999995E-2</v>
       </c>
       <c r="H11" s="15">
         <f>SUM(H2:H9)</f>
-        <v>0.36150000000000004</v>
-      </c>
-      <c r="I11" s="15">
-        <f>SUM(I2:I9)</f>
-        <v>0.54350000000000009</v>
+        <v>0.58800000000000008</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2">
         <v>0.6</v>
       </c>
       <c r="C14" s="2">
-        <v>0.7</v>
+        <f>K$2</f>
+        <v>0.3</v>
       </c>
       <c r="D14" s="2">
+        <f>L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E14" s="2">
         <v>0.1</v>
       </c>
-      <c r="E14" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F14" s="2">
         <v>0.3</v>
       </c>
       <c r="G14" s="13">
-        <f>B14*C14*D14</f>
-        <v>4.2000000000000003E-2</v>
+        <f>B14*C14*E14</f>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H14" s="13">
-        <f>B14*C14*E14</f>
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="I14" s="13">
-        <f>B14*C14*F14</f>
+        <f>B14*D14*F14</f>
         <v>0.126</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2">
         <v>0.4</v>
       </c>
       <c r="C15" s="2">
+        <f t="shared" ref="C15:D23" si="3">K$2</f>
         <v>0.3</v>
       </c>
       <c r="D15" s="2">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="E15" s="2">
         <v>0.1</v>
       </c>
-      <c r="E15" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F15" s="2">
         <v>0.3</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" ref="G15:G23" si="2">B15*C15*D15</f>
+        <f>B15*C15*E15</f>
         <v>1.2E-2</v>
       </c>
       <c r="H15" s="13">
-        <f>B15*C15*E15</f>
-        <v>2.4E-2</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" ref="I15:I23" si="3">B15*C15*F15</f>
-        <v>3.5999999999999997E-2</v>
+        <f t="shared" ref="H15:H23" si="4">B15*D15*F15</f>
+        <v>8.3999999999999991E-2</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B16" s="2">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="C16" s="2">
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.3</v>
       </c>
       <c r="D16" s="2">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="E16" s="2">
         <v>0.1</v>
       </c>
-      <c r="E16" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F16" s="2">
         <v>0.3</v>
       </c>
       <c r="G16" s="13">
-        <f t="shared" si="2"/>
-        <v>0.03</v>
+        <f>B16*C16*E16</f>
+        <v>1.2E-2</v>
       </c>
       <c r="H16" s="13">
-        <f>B16*C16*E16</f>
-        <v>0.06</v>
-      </c>
-      <c r="I16" s="13">
-        <f t="shared" si="3"/>
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>8.3999999999999991E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2">
         <v>0.2</v>
       </c>
       <c r="C17" s="2">
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0.3</v>
       </c>
       <c r="D17" s="2">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="E17" s="2">
         <v>0.1</v>
       </c>
-      <c r="E17" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F17" s="2">
         <v>0.3</v>
       </c>
       <c r="G17" s="13">
-        <f t="shared" si="2"/>
-        <v>1.6000000000000004E-2</v>
+        <f>B17*C17*E17</f>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="H17" s="13">
-        <f>B17*C17*E17</f>
-        <v>3.2000000000000008E-2</v>
-      </c>
-      <c r="I17" s="13">
-        <f t="shared" si="3"/>
-        <v>4.8000000000000008E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>4.1999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2">
         <v>0.2</v>
       </c>
       <c r="C18" s="2">
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0.3</v>
       </c>
       <c r="D18" s="2">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="E18" s="2">
         <v>0.1</v>
       </c>
-      <c r="E18" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F18" s="2">
         <v>0.3</v>
       </c>
       <c r="G18" s="13">
-        <f t="shared" si="2"/>
-        <v>1.6000000000000004E-2</v>
+        <f>B18*C18*E18</f>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="H18" s="13">
-        <f>B18*C18*E18</f>
-        <v>3.2000000000000008E-2</v>
-      </c>
-      <c r="I18" s="13">
-        <f t="shared" si="3"/>
-        <v>4.8000000000000008E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>4.1999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2">
         <v>0.2</v>
       </c>
       <c r="C19" s="2">
-        <v>0.6</v>
+        <f t="shared" si="3"/>
+        <v>0.3</v>
       </c>
       <c r="D19" s="2">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="E19" s="2">
         <v>0.1</v>
       </c>
-      <c r="E19" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F19" s="2">
         <v>0.3</v>
       </c>
       <c r="G19" s="13">
-        <f t="shared" si="2"/>
-        <v>1.2E-2</v>
+        <f>B19*C19*E19</f>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="H19" s="13">
-        <f>B19*C19*E19</f>
-        <v>2.4E-2</v>
-      </c>
-      <c r="I19" s="13">
+        <f t="shared" si="4"/>
+        <v>4.1999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C20" s="2">
         <f t="shared" si="3"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0.85</v>
+        <v>0.3</v>
       </c>
       <c r="D20" s="2">
-        <v>0.3</v>
+        <f t="shared" si="3"/>
+        <v>0.7</v>
       </c>
       <c r="E20" s="2">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F20" s="2">
         <v>0.9</v>
       </c>
       <c r="G20" s="13">
-        <f t="shared" si="2"/>
-        <v>7.6499999999999999E-2</v>
+        <f>B20*C20*E20</f>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="H20" s="13">
-        <f>B20*C20*E20</f>
-        <v>0.153</v>
-      </c>
-      <c r="I20" s="13">
-        <f t="shared" si="3"/>
-        <v>0.22950000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0.189</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B21" s="2">
         <v>0.5</v>
       </c>
       <c r="C21" s="2">
+        <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
       <c r="D21" s="2">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="E21" s="2">
         <v>0.1</v>
       </c>
-      <c r="E21" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F21" s="2">
         <v>0.3</v>
       </c>
       <c r="G21" s="13">
-        <f t="shared" si="2"/>
+        <f>B21*C21*E21</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="H21" s="13">
-        <f>B21*C21*E21</f>
-        <v>0.03</v>
-      </c>
-      <c r="I21" s="13">
-        <f t="shared" si="3"/>
-        <v>4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2">
         <v>0.25</v>
       </c>
       <c r="C22" s="2">
-        <v>0.6</v>
+        <f t="shared" si="3"/>
+        <v>0.3</v>
       </c>
       <c r="D22" s="2">
+        <f>L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E22" s="2">
         <v>0.05</v>
       </c>
-      <c r="E22" s="2">
-        <v>0.1</v>
-      </c>
       <c r="F22" s="2">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="G22" s="13">
-        <f t="shared" si="2"/>
-        <v>7.4999999999999997E-3</v>
+        <f>B22*C22*E22</f>
+        <v>3.7499999999999999E-3</v>
       </c>
       <c r="H22" s="13">
-        <f>B22*C22*E22</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="I22" s="13">
-        <f t="shared" si="3"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>2.6249999999999999E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2">
         <v>0.2</v>
       </c>
       <c r="C23" s="2">
-        <v>0.4</v>
+        <f t="shared" si="3"/>
+        <v>0.3</v>
       </c>
       <c r="D23" s="2">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="E23" s="2">
         <v>0.1</v>
       </c>
-      <c r="E23" s="2">
-        <v>0.2</v>
-      </c>
       <c r="F23" s="2">
         <v>0.3</v>
       </c>
       <c r="G23" s="13">
-        <f t="shared" si="2"/>
-        <v>8.0000000000000019E-3</v>
+        <f>B23*C23*E23</f>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="H23" s="13">
-        <f>B23*C23*E23</f>
-        <v>1.6000000000000004E-2</v>
-      </c>
-      <c r="I23" s="13">
-        <f t="shared" si="3"/>
-        <v>2.4000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>4.1999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G24" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D25" s="1"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E25" s="1"/>
       <c r="F25" s="14" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G25" s="15">
         <f>SUM(G14:G23)</f>
-        <v>0.23500000000000004</v>
+        <v>0.12974999999999998</v>
       </c>
       <c r="H25" s="15">
         <f>SUM(H14:H23)</f>
-        <v>0.47000000000000008</v>
-      </c>
-      <c r="I25" s="15">
-        <f>SUM(I14:I23)</f>
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.78225</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>113</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B29" s="17">
         <v>0.4</v>
       </c>
-      <c r="C29" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="D29" s="17">
+      <c r="C29" s="2">
+        <f>K$2</f>
+        <v>0.3</v>
+      </c>
+      <c r="D29" s="2">
+        <f>L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E29" s="17">
         <v>0.1</v>
       </c>
-      <c r="E29" s="17">
-        <v>0.2</v>
-      </c>
       <c r="F29" s="17">
         <v>0.3</v>
       </c>
       <c r="G29" s="13">
-        <f>B29*C29*D29</f>
-        <v>2.0000000000000004E-2</v>
+        <f>B29*C29*E29</f>
+        <v>1.2E-2</v>
       </c>
       <c r="H29" s="13">
-        <f>B29*C29*E29</f>
-        <v>4.0000000000000008E-2</v>
-      </c>
-      <c r="I29" s="13">
-        <f>B29*C29*F29</f>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <f>B29*D29*F29</f>
+        <v>8.3999999999999991E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B30" s="17">
         <v>0.25</v>
       </c>
-      <c r="C30" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="D30" s="17">
+      <c r="C30" s="2">
+        <f t="shared" ref="C30:D38" si="5">K$2</f>
+        <v>0.3</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="E30" s="17">
         <v>0.1</v>
       </c>
-      <c r="E30" s="17">
-        <v>0.2</v>
-      </c>
       <c r="F30" s="17">
         <v>0.3</v>
       </c>
       <c r="G30" s="13">
-        <f t="shared" ref="G30:G37" si="4">B30*C30*D30</f>
-        <v>1.7499999999999998E-2</v>
+        <f>B30*C30*E30</f>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="H30" s="13">
-        <f t="shared" ref="H30:I37" si="5">B30*C30*E30</f>
-        <v>3.4999999999999996E-2</v>
-      </c>
-      <c r="I30" s="13">
-        <f t="shared" ref="I30:I37" si="6">B30*C30*F30</f>
+        <f t="shared" ref="H30:H37" si="6">B30*D30*F30</f>
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B31" s="17">
         <v>0.3</v>
       </c>
-      <c r="C31" s="17">
-        <v>0.8</v>
-      </c>
-      <c r="D31" s="17">
-        <v>0.3</v>
+      <c r="C31" s="2">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
       </c>
       <c r="E31" s="17">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F31" s="17">
         <v>0.9</v>
       </c>
       <c r="G31" s="13">
-        <f t="shared" si="4"/>
-        <v>7.1999999999999995E-2</v>
+        <f>B31*C31*E31</f>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="H31" s="13">
-        <f t="shared" si="5"/>
-        <v>0.14399999999999999</v>
-      </c>
-      <c r="I31" s="13">
         <f t="shared" si="6"/>
-        <v>0.216</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.189</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B32" s="17">
         <v>0.9</v>
       </c>
-      <c r="C32" s="17">
-        <v>0.15</v>
-      </c>
-      <c r="D32" s="17">
-        <v>0.3</v>
+      <c r="C32" s="2">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
       </c>
       <c r="E32" s="17">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="F32" s="17">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="G32" s="13">
-        <f t="shared" si="4"/>
-        <v>4.0500000000000001E-2</v>
+        <f>B32*C32*E32</f>
+        <v>1.3500000000000002E-2</v>
       </c>
       <c r="H32" s="13">
-        <f t="shared" si="5"/>
-        <v>8.1000000000000003E-2</v>
-      </c>
-      <c r="I32" s="13">
         <f t="shared" si="6"/>
-        <v>0.12150000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B33" s="17">
         <v>0.25</v>
       </c>
-      <c r="C33" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="D33" s="17">
+      <c r="C33" s="2">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="D33" s="2">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="E33" s="17">
         <v>0.05</v>
       </c>
-      <c r="E33" s="17">
-        <v>0.1</v>
-      </c>
       <c r="F33" s="17">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G33" s="13">
-        <f t="shared" si="4"/>
-        <v>7.4999999999999997E-3</v>
+        <f>B33*C33*E33</f>
+        <v>3.7499999999999999E-3</v>
       </c>
       <c r="H33" s="13">
-        <f t="shared" si="5"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="I33" s="13">
         <f t="shared" si="6"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3.4999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B34" s="17">
         <v>0.4</v>
       </c>
-      <c r="C34" s="17">
-        <v>0.4</v>
-      </c>
-      <c r="D34" s="17">
+      <c r="C34" s="2">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="E34" s="17">
         <v>0.1</v>
       </c>
-      <c r="E34" s="17">
-        <v>0.2</v>
-      </c>
       <c r="F34" s="17">
         <v>0.3</v>
       </c>
       <c r="G34" s="13">
-        <f t="shared" si="4"/>
-        <v>1.6000000000000004E-2</v>
+        <f>B34*C34*E34</f>
+        <v>1.2E-2</v>
       </c>
       <c r="H34" s="13">
+        <f t="shared" si="6"/>
+        <v>8.3999999999999991E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="C35" s="2">
         <f t="shared" si="5"/>
-        <v>3.2000000000000008E-2</v>
-      </c>
-      <c r="I34" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="E35" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="F35" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G35" s="13">
+        <f>B35*C35*E35</f>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H35" s="13">
         <f t="shared" si="6"/>
-        <v>4.8000000000000008E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="C35" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="D35" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="E35" s="17">
-        <v>0.2</v>
-      </c>
-      <c r="F35" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="G35" s="13">
-        <f t="shared" si="4"/>
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="H35" s="13">
-        <f t="shared" si="5"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="I35" s="13">
-        <f t="shared" si="6"/>
-        <v>5.3999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B36" s="17">
         <v>0.25</v>
       </c>
-      <c r="C36" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="D36" s="17">
+      <c r="C36" s="2">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="E36" s="17">
         <v>0.1</v>
       </c>
-      <c r="E36" s="17">
-        <v>0.2</v>
-      </c>
       <c r="F36" s="17">
         <v>0.3</v>
       </c>
       <c r="G36" s="13">
-        <f t="shared" si="4"/>
-        <v>1.7499999999999998E-2</v>
+        <f>B36*C36*E36</f>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="H36" s="13">
-        <f t="shared" si="5"/>
-        <v>3.4999999999999996E-2</v>
-      </c>
-      <c r="I36" s="13">
         <f t="shared" si="6"/>
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B37" s="17">
         <v>0.2</v>
       </c>
-      <c r="C37" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="D37" s="17">
-        <v>0.3</v>
+      <c r="C37" s="2">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="D37" s="2">
+        <f>L$2</f>
+        <v>0.7</v>
       </c>
       <c r="E37" s="17">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F37" s="17">
         <v>0.9</v>
       </c>
       <c r="G37" s="13">
-        <f t="shared" si="4"/>
-        <v>3.5999999999999997E-2</v>
+        <f>B37*C37*E37</f>
+        <v>0.03</v>
       </c>
       <c r="H37" s="13">
-        <f t="shared" si="5"/>
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="I37" s="13">
         <f t="shared" si="6"/>
-        <v>0.108</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
+      <c r="C38" s="2"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="G38" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
       <c r="D39" s="17"/>
       <c r="E39" s="18"/>
       <c r="F39" s="14" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G39" s="15">
         <f>SUM(G28:G37)</f>
-        <v>0.245</v>
+        <v>0.14024999999999999</v>
       </c>
       <c r="H39" s="15">
         <f>SUM(H28:H37)</f>
-        <v>0.49</v>
-      </c>
-      <c r="I39" s="15">
-        <f>SUM(I28:I37)</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.749</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
       <c r="E41" s="18"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
       <c r="D42" s="17"/>
       <c r="E42" s="18"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
       <c r="E43" s="18"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
       <c r="D44" s="17"/>
       <c r="E44" s="18"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
       <c r="D45" s="17"/>
       <c r="E45" s="18"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
       <c r="D46" s="17"/>
       <c r="E46" s="18"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
       <c r="D47" s="17"/>
       <c r="E47" s="18"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>

--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="119">
   <si>
     <t>Сектор</t>
   </si>
@@ -325,18 +325,12 @@
     <t>Автоматизация и повышение производительности финансовых операций</t>
   </si>
   <si>
-    <t>ФАКТОРЫ ВДС (Сектор А)</t>
-  </si>
-  <si>
     <t>Significance</t>
   </si>
   <si>
     <t>Total =</t>
   </si>
   <si>
-    <t>Сектор В</t>
-  </si>
-  <si>
     <t>Impact (max)</t>
   </si>
   <si>
@@ -355,9 +349,6 @@
     <t>Index (max)</t>
   </si>
   <si>
-    <t>Сектор C</t>
-  </si>
-  <si>
     <t>Capabilty (min)</t>
   </si>
   <si>
@@ -368,13 +359,31 @@
   </si>
   <si>
     <t>5-10%</t>
+  </si>
+  <si>
+    <t>Сектор F (Строительство)</t>
+  </si>
+  <si>
+    <t>Сектор C (Производство</t>
+  </si>
+  <si>
+    <t>Сектор В (Добыча)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФАКТОРЫ ВДС (Сектор А - Сельхоз) </t>
+  </si>
+  <si>
+    <t>Сектор G (Торговля)</t>
+  </si>
+  <si>
+    <t>Сектор J (Информация и связь)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -406,6 +415,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -462,10 +478,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -507,9 +524,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -517,9 +531,16 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Процентный" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1125,7 +1146,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1165,7 +1186,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1173,7 +1194,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1181,7 +1202,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1192,7 +1213,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -1210,34 +1231,34 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -1262,7 +1283,7 @@
         <v>0.3</v>
       </c>
       <c r="G2" s="13">
-        <f>B2*C2*E2</f>
+        <f t="shared" ref="G2:G9" si="0">B2*C2*E2</f>
         <v>1.2E-2</v>
       </c>
       <c r="H2" s="13">
@@ -1287,11 +1308,11 @@
         <v>0.3</v>
       </c>
       <c r="C3" s="2">
-        <f t="shared" ref="C3:C9" si="0">K$2</f>
+        <f t="shared" ref="C3:C9" si="1">K$2</f>
         <v>0.3</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D9" si="1">L$2</f>
+        <f t="shared" ref="D3:D9" si="2">L$2</f>
         <v>0.7</v>
       </c>
       <c r="E3" s="2">
@@ -1301,11 +1322,11 @@
         <v>0.3</v>
       </c>
       <c r="G3" s="13">
-        <f>B3*C3*E3</f>
+        <f t="shared" si="0"/>
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="H3" s="13">
-        <f t="shared" ref="H3:H9" si="2">B3*D3*F3</f>
+        <f t="shared" ref="H3:H9" si="3">B3*D3*F3</f>
         <v>6.3E-2</v>
       </c>
       <c r="J3" s="2"/>
@@ -1321,11 +1342,11 @@
         <v>0.9</v>
       </c>
       <c r="C4" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
       <c r="E4" s="2">
@@ -1335,11 +1356,11 @@
         <v>0.1</v>
       </c>
       <c r="G4" s="13">
-        <f>B4*C4*E4</f>
+        <f t="shared" si="0"/>
         <v>1.3500000000000002E-2</v>
       </c>
       <c r="H4" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.3E-2</v>
       </c>
       <c r="J4" s="2"/>
@@ -1355,25 +1376,25 @@
         <v>0.25</v>
       </c>
       <c r="C5" s="2">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="2"/>
+        <v>0.7</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="13">
         <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="D5" s="2">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="G5" s="13">
-        <f>B5*C5*E5</f>
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="H5" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.2499999999999998E-2</v>
       </c>
       <c r="J5" s="2"/>
@@ -1389,25 +1410,25 @@
         <v>0.4</v>
       </c>
       <c r="C6" s="2">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="2"/>
+        <v>0.7</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G6" s="13">
         <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="D6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="G6" s="13">
-        <f>B6*C6*E6</f>
         <v>1.2E-2</v>
       </c>
       <c r="H6" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.3999999999999991E-2</v>
       </c>
       <c r="J6" s="2"/>
@@ -1423,25 +1444,25 @@
         <v>0.3</v>
       </c>
       <c r="C7" s="2">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="2"/>
+        <v>0.7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="13">
         <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="D7" s="2">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="G7" s="13">
-        <f>B7*C7*E7</f>
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="H7" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.3E-2</v>
       </c>
       <c r="J7" s="2"/>
@@ -1457,25 +1478,25 @@
         <v>0.6</v>
       </c>
       <c r="C8" s="2">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="2"/>
+        <v>0.7</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="13">
         <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="G8" s="13">
-        <f>B8*C8*E8</f>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="H8" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.126</v>
       </c>
       <c r="J8" s="2"/>
@@ -1491,25 +1512,25 @@
         <v>0.25</v>
       </c>
       <c r="C9" s="2">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="2"/>
+        <v>0.7</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="13">
         <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="D9" s="2">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="G9" s="13">
-        <f>B9*C9*E9</f>
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="H9" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.2499999999999998E-2</v>
       </c>
       <c r="J9" s="2"/>
@@ -1519,51 +1540,51 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G10" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F11" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="G11" s="15">
+        <v>102</v>
+      </c>
+      <c r="G11" s="18">
         <f>SUM(G2:G9)</f>
         <v>8.8499999999999995E-2</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="18">
         <f>SUM(H2:H9)</f>
         <v>0.58800000000000008</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="F13" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1588,7 +1609,7 @@
         <v>0.3</v>
       </c>
       <c r="G14" s="13">
-        <f>B14*C14*E14</f>
+        <f t="shared" ref="G14:G23" si="4">B14*C14*E14</f>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="H14" s="13">
@@ -1604,11 +1625,11 @@
         <v>0.4</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" ref="C15:D23" si="3">K$2</f>
+        <f t="shared" ref="C15:D23" si="5">K$2</f>
         <v>0.3</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
       <c r="E15" s="2">
@@ -1618,11 +1639,11 @@
         <v>0.3</v>
       </c>
       <c r="G15" s="13">
-        <f>B15*C15*E15</f>
+        <f t="shared" si="4"/>
         <v>1.2E-2</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" ref="H15:H23" si="4">B15*D15*F15</f>
+        <f t="shared" ref="H15:H23" si="6">B15*D15*F15</f>
         <v>8.3999999999999991E-2</v>
       </c>
     </row>
@@ -1634,11 +1655,11 @@
         <v>0.4</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
       <c r="E16" s="2">
@@ -1648,11 +1669,11 @@
         <v>0.3</v>
       </c>
       <c r="G16" s="13">
-        <f>B16*C16*E16</f>
+        <f t="shared" si="4"/>
         <v>1.2E-2</v>
       </c>
       <c r="H16" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8.3999999999999991E-2</v>
       </c>
     </row>
@@ -1664,11 +1685,11 @@
         <v>0.2</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="D17" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
       <c r="E17" s="2">
@@ -1678,11 +1699,11 @@
         <v>0.3</v>
       </c>
       <c r="G17" s="13">
-        <f>B17*C17*E17</f>
+        <f t="shared" si="4"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="H17" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.1999999999999996E-2</v>
       </c>
     </row>
@@ -1694,11 +1715,11 @@
         <v>0.2</v>
       </c>
       <c r="C18" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="D18" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
       <c r="E18" s="2">
@@ -1708,11 +1729,11 @@
         <v>0.3</v>
       </c>
       <c r="G18" s="13">
-        <f>B18*C18*E18</f>
+        <f t="shared" si="4"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="H18" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.1999999999999996E-2</v>
       </c>
     </row>
@@ -1724,11 +1745,11 @@
         <v>0.2</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="D19" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
       <c r="E19" s="2">
@@ -1738,11 +1759,11 @@
         <v>0.3</v>
       </c>
       <c r="G19" s="13">
-        <f>B19*C19*E19</f>
+        <f t="shared" si="4"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="H19" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.1999999999999996E-2</v>
       </c>
     </row>
@@ -1754,11 +1775,11 @@
         <v>0.3</v>
       </c>
       <c r="C20" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="D20" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
       <c r="E20" s="2">
@@ -1768,11 +1789,11 @@
         <v>0.9</v>
       </c>
       <c r="G20" s="13">
-        <f>B20*C20*E20</f>
+        <f t="shared" si="4"/>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="H20" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.189</v>
       </c>
     </row>
@@ -1784,11 +1805,11 @@
         <v>0.5</v>
       </c>
       <c r="C21" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
       <c r="E21" s="2">
@@ -1798,11 +1819,11 @@
         <v>0.3</v>
       </c>
       <c r="G21" s="13">
-        <f>B21*C21*E21</f>
+        <f t="shared" si="4"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="H21" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.105</v>
       </c>
     </row>
@@ -1814,7 +1835,7 @@
         <v>0.25</v>
       </c>
       <c r="C22" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="D22" s="2">
@@ -1828,11 +1849,11 @@
         <v>0.15</v>
       </c>
       <c r="G22" s="13">
-        <f>B22*C22*E22</f>
+        <f t="shared" si="4"/>
         <v>3.7499999999999999E-3</v>
       </c>
       <c r="H22" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.6249999999999999E-2</v>
       </c>
     </row>
@@ -1844,11 +1865,11 @@
         <v>0.2</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="D23" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
       <c r="E23" s="2">
@@ -1858,67 +1879,67 @@
         <v>0.3</v>
       </c>
       <c r="G23" s="13">
-        <f>B23*C23*E23</f>
+        <f t="shared" si="4"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="H23" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.1999999999999996E-2</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G24" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E25" s="1"/>
       <c r="F25" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="G25" s="15">
+        <v>102</v>
+      </c>
+      <c r="G25" s="18">
         <f>SUM(G14:G23)</f>
         <v>0.12974999999999998</v>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="18">
         <f>SUM(H14:H23)</f>
         <v>0.78225</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="H28" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="16">
         <v>0.4</v>
       </c>
       <c r="C29" s="2">
@@ -1929,14 +1950,14 @@
         <f>L$2</f>
         <v>0.7</v>
       </c>
-      <c r="E29" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="F29" s="17">
+      <c r="E29" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F29" s="16">
         <v>0.3</v>
       </c>
       <c r="G29" s="13">
-        <f>B29*C29*E29</f>
+        <f t="shared" ref="G29:G37" si="7">B29*C29*E29</f>
         <v>1.2E-2</v>
       </c>
       <c r="H29" s="13">
@@ -1948,29 +1969,29 @@
       <c r="A30" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="16">
         <v>0.25</v>
       </c>
       <c r="C30" s="2">
-        <f t="shared" ref="C30:D38" si="5">K$2</f>
+        <f t="shared" ref="C30:D37" si="8">K$2</f>
         <v>0.3</v>
       </c>
       <c r="D30" s="2">
-        <f t="shared" si="5"/>
-        <v>0.7</v>
-      </c>
-      <c r="E30" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="F30" s="17">
+        <f t="shared" si="8"/>
+        <v>0.7</v>
+      </c>
+      <c r="E30" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F30" s="16">
         <v>0.3</v>
       </c>
       <c r="G30" s="13">
-        <f>B30*C30*E30</f>
+        <f t="shared" si="7"/>
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="H30" s="13">
-        <f t="shared" ref="H30:H37" si="6">B30*D30*F30</f>
+        <f t="shared" ref="H30:H37" si="9">B30*D30*F30</f>
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
@@ -1978,29 +1999,29 @@
       <c r="A31" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="16">
         <v>0.3</v>
       </c>
       <c r="C31" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.3</v>
       </c>
       <c r="D31" s="2">
-        <f t="shared" si="5"/>
-        <v>0.7</v>
-      </c>
-      <c r="E31" s="17">
+        <f t="shared" si="8"/>
+        <v>0.7</v>
+      </c>
+      <c r="E31" s="16">
         <v>0.5</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="16">
         <v>0.9</v>
       </c>
       <c r="G31" s="13">
-        <f>B31*C31*E31</f>
+        <f t="shared" si="7"/>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="H31" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.189</v>
       </c>
     </row>
@@ -2008,29 +2029,29 @@
       <c r="A32" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="16">
         <v>0.9</v>
       </c>
       <c r="C32" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.3</v>
       </c>
       <c r="D32" s="2">
-        <f t="shared" si="5"/>
-        <v>0.7</v>
-      </c>
-      <c r="E32" s="17">
+        <f t="shared" si="8"/>
+        <v>0.7</v>
+      </c>
+      <c r="E32" s="16">
         <v>0.05</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="16">
         <v>0.1</v>
       </c>
       <c r="G32" s="13">
-        <f>B32*C32*E32</f>
+        <f t="shared" si="7"/>
         <v>1.3500000000000002E-2</v>
       </c>
       <c r="H32" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>6.3E-2</v>
       </c>
     </row>
@@ -2038,29 +2059,29 @@
       <c r="A33" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="16">
         <v>0.25</v>
       </c>
       <c r="C33" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.3</v>
       </c>
       <c r="D33" s="2">
-        <f t="shared" si="5"/>
-        <v>0.7</v>
-      </c>
-      <c r="E33" s="17">
+        <f t="shared" si="8"/>
+        <v>0.7</v>
+      </c>
+      <c r="E33" s="16">
         <v>0.05</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="16">
         <v>0.2</v>
       </c>
       <c r="G33" s="13">
-        <f>B33*C33*E33</f>
+        <f t="shared" si="7"/>
         <v>3.7499999999999999E-3</v>
       </c>
       <c r="H33" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.4999999999999996E-2</v>
       </c>
     </row>
@@ -2068,29 +2089,29 @@
       <c r="A34" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="16">
         <v>0.4</v>
       </c>
       <c r="C34" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.3</v>
       </c>
       <c r="D34" s="2">
-        <f t="shared" si="5"/>
-        <v>0.7</v>
-      </c>
-      <c r="E34" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="F34" s="17">
+        <f t="shared" si="8"/>
+        <v>0.7</v>
+      </c>
+      <c r="E34" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F34" s="16">
         <v>0.3</v>
       </c>
       <c r="G34" s="13">
-        <f>B34*C34*E34</f>
+        <f t="shared" si="7"/>
         <v>1.2E-2</v>
       </c>
       <c r="H34" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>8.3999999999999991E-2</v>
       </c>
     </row>
@@ -2098,29 +2119,29 @@
       <c r="A35" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="16">
         <v>0.3</v>
       </c>
       <c r="C35" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.3</v>
       </c>
       <c r="D35" s="2">
-        <f t="shared" si="5"/>
-        <v>0.7</v>
-      </c>
-      <c r="E35" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="F35" s="17">
+        <f t="shared" si="8"/>
+        <v>0.7</v>
+      </c>
+      <c r="E35" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F35" s="16">
         <v>0.3</v>
       </c>
       <c r="G35" s="13">
-        <f>B35*C35*E35</f>
+        <f t="shared" si="7"/>
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="H35" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>6.3E-2</v>
       </c>
     </row>
@@ -2128,29 +2149,29 @@
       <c r="A36" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="16">
         <v>0.25</v>
       </c>
       <c r="C36" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.3</v>
       </c>
       <c r="D36" s="2">
-        <f t="shared" si="5"/>
-        <v>0.7</v>
-      </c>
-      <c r="E36" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="F36" s="17">
+        <f t="shared" si="8"/>
+        <v>0.7</v>
+      </c>
+      <c r="E36" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F36" s="16">
         <v>0.3</v>
       </c>
       <c r="G36" s="13">
-        <f>B36*C36*E36</f>
+        <f t="shared" si="7"/>
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="H36" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
@@ -2158,159 +2179,886 @@
       <c r="A37" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="16">
         <v>0.2</v>
       </c>
       <c r="C37" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.3</v>
       </c>
       <c r="D37" s="2">
         <f>L$2</f>
         <v>0.7</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="16">
         <v>0.5</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="16">
         <v>0.9</v>
       </c>
       <c r="G37" s="13">
-        <f>B37*C37*E37</f>
+        <f t="shared" si="7"/>
         <v>0.03</v>
       </c>
       <c r="H37" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.126</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="16"/>
+      <c r="B38" s="15"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
       <c r="G38" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="15"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G39" s="19">
+        <f>SUM(G29:G37)</f>
+        <v>0.14024999999999999</v>
+      </c>
+      <c r="H39" s="19">
+        <f>SUM(H29:H37)</f>
+        <v>0.749</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="16"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H38" s="1" t="s">
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="C42" s="2">
+        <f>K$2</f>
+        <v>0.3</v>
+      </c>
+      <c r="D42" s="2">
+        <f>L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E42" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F42" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G42" s="13">
+        <f t="shared" ref="G42:G50" si="10">B42*C42*E42</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H42" s="13">
+        <f>B42*D42*F42</f>
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="C43" s="2">
+        <f t="shared" ref="C43:C50" si="11">K$2</f>
+        <v>0.3</v>
+      </c>
+      <c r="D43" s="2">
+        <f t="shared" ref="D43:D50" si="12">L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E43" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F43" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G43" s="13">
+        <f t="shared" si="10"/>
+        <v>1.2E-2</v>
+      </c>
+      <c r="H43" s="13">
+        <f t="shared" ref="H43:H50" si="13">B43*D43*F43</f>
+        <v>8.3999999999999991E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="C44" s="2">
+        <f t="shared" si="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="D44" s="2">
+        <f t="shared" si="12"/>
+        <v>0.7</v>
+      </c>
+      <c r="E44" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F44" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G44" s="13">
+        <f t="shared" si="10"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H44" s="13">
+        <f t="shared" si="13"/>
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="C45" s="2">
+        <f t="shared" si="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="D45" s="2">
+        <f t="shared" si="12"/>
+        <v>0.7</v>
+      </c>
+      <c r="E45" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F45" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G45" s="13">
+        <f t="shared" si="10"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H45" s="13">
+        <f t="shared" si="13"/>
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="C46" s="2">
+        <f t="shared" si="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="D46" s="2">
+        <f t="shared" si="12"/>
+        <v>0.7</v>
+      </c>
+      <c r="E46" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F46" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G46" s="13">
+        <f t="shared" si="10"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H46" s="13">
+        <f t="shared" si="13"/>
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="C47" s="2">
+        <f t="shared" si="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="D47" s="2">
+        <f t="shared" si="12"/>
+        <v>0.7</v>
+      </c>
+      <c r="E47" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F47" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="G47" s="13">
+        <f t="shared" si="10"/>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H47" s="13">
+        <f t="shared" si="13"/>
+        <v>0.189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="C48" s="2">
+        <f t="shared" si="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="D48" s="2">
+        <f t="shared" si="12"/>
+        <v>0.7</v>
+      </c>
+      <c r="E48" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F48" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G48" s="13">
+        <f t="shared" si="10"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H48" s="13">
+        <f t="shared" si="13"/>
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="C49" s="2">
+        <f t="shared" si="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="D49" s="2">
+        <f t="shared" si="12"/>
+        <v>0.7</v>
+      </c>
+      <c r="E49" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="F49" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="G49" s="13">
+        <f t="shared" si="10"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="H49" s="13">
+        <f t="shared" si="13"/>
+        <v>5.5999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="C50" s="2">
+        <f t="shared" si="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="D50" s="2">
+        <f>L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E50" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F50" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G50" s="13">
+        <f t="shared" si="10"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H50" s="13">
+        <f t="shared" si="13"/>
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="15"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="G51" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="15"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G52" s="18">
+        <f>SUM(G42:G50)</f>
+        <v>0.129</v>
+      </c>
+      <c r="H52" s="18">
+        <f>SUM(H42:H50)</f>
+        <v>0.79099999999999993</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="15"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="17"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="16"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="14" t="s">
+      <c r="D54" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G39" s="15">
-        <f>SUM(G28:G37)</f>
-        <v>0.14024999999999999</v>
-      </c>
-      <c r="H39" s="15">
-        <f>SUM(H28:H37)</f>
-        <v>0.749</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="18"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="18"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="18"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="18"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="18"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="18"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="18"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="18"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="18"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="18"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="16"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="16"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="18"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="16"/>
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="18"/>
+      <c r="G54" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C55" s="2">
+        <f>K$2</f>
+        <v>0.3</v>
+      </c>
+      <c r="D55" s="2">
+        <f>L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E55" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F55" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G55" s="13">
+        <f t="shared" ref="G55:G61" si="14">B55*C55*E55</f>
+        <v>1.2E-2</v>
+      </c>
+      <c r="H55" s="13">
+        <f>B55*D55*F55</f>
+        <v>8.3999999999999991E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C56" s="2">
+        <f t="shared" ref="C56:C60" si="15">K$2</f>
+        <v>0.3</v>
+      </c>
+      <c r="D56" s="2">
+        <f t="shared" ref="D56:D60" si="16">L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E56" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F56" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G56" s="13">
+        <f t="shared" si="14"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H56" s="13">
+        <f t="shared" ref="H56:H61" si="17">B56*D56*F56</f>
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C57" s="2">
+        <f t="shared" si="15"/>
+        <v>0.3</v>
+      </c>
+      <c r="D57" s="2">
+        <f t="shared" si="16"/>
+        <v>0.7</v>
+      </c>
+      <c r="E57" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F57" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G57" s="13">
+        <f t="shared" si="14"/>
+        <v>1.2E-2</v>
+      </c>
+      <c r="H57" s="13">
+        <f t="shared" si="17"/>
+        <v>8.3999999999999991E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C58" s="2">
+        <f t="shared" si="15"/>
+        <v>0.3</v>
+      </c>
+      <c r="D58" s="2">
+        <f t="shared" si="16"/>
+        <v>0.7</v>
+      </c>
+      <c r="E58" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F58" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G58" s="13">
+        <f t="shared" si="14"/>
+        <v>1.2E-2</v>
+      </c>
+      <c r="H58" s="13">
+        <f t="shared" si="17"/>
+        <v>8.3999999999999991E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="C59" s="2">
+        <f t="shared" si="15"/>
+        <v>0.3</v>
+      </c>
+      <c r="D59" s="2">
+        <f t="shared" si="16"/>
+        <v>0.7</v>
+      </c>
+      <c r="E59" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F59" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G59" s="13">
+        <f t="shared" si="14"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="H59" s="13">
+        <f t="shared" si="17"/>
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C60" s="2">
+        <f t="shared" si="15"/>
+        <v>0.3</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" si="16"/>
+        <v>0.7</v>
+      </c>
+      <c r="E60" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F60" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G60" s="13">
+        <f t="shared" si="14"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H60" s="13">
+        <f t="shared" si="17"/>
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C61" s="2">
+        <f t="shared" ref="C61" si="18">K$2</f>
+        <v>0.3</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" ref="D61" si="19">L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E61" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F61" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G61" s="13">
+        <f t="shared" si="14"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H61" s="13">
+        <f t="shared" si="17"/>
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G62" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F63" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G63" s="18">
+        <f>SUM(G55:G61)</f>
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="H63" s="18">
+        <f>SUM(H55:H61)</f>
+        <v>0.65100000000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="C66" s="2">
+        <f>K$2</f>
+        <v>0.3</v>
+      </c>
+      <c r="D66" s="2">
+        <f>L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E66" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F66" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G66" s="13">
+        <f t="shared" ref="G66:G70" si="20">B66*C66*E66</f>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="H66" s="13">
+        <f>B66*D66*F66</f>
+        <v>0.14699999999999996</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C67" s="2">
+        <f t="shared" ref="C67:C71" si="21">K$2</f>
+        <v>0.3</v>
+      </c>
+      <c r="D67" s="2">
+        <f t="shared" ref="D67:D71" si="22">L$2</f>
+        <v>0.7</v>
+      </c>
+      <c r="E67" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F67" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G67" s="13">
+        <f t="shared" si="20"/>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="H67" s="13">
+        <f t="shared" ref="H67:H70" si="23">B67*D67*F67</f>
+        <v>5.2499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C68" s="2">
+        <f t="shared" si="21"/>
+        <v>0.3</v>
+      </c>
+      <c r="D68" s="2">
+        <f t="shared" si="22"/>
+        <v>0.7</v>
+      </c>
+      <c r="E68" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F68" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G68" s="13">
+        <f t="shared" si="20"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H68" s="13">
+        <f t="shared" si="23"/>
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B69" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C69" s="2">
+        <f t="shared" si="21"/>
+        <v>0.3</v>
+      </c>
+      <c r="D69" s="2">
+        <f t="shared" si="22"/>
+        <v>0.7</v>
+      </c>
+      <c r="E69" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F69" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G69" s="13">
+        <f t="shared" si="20"/>
+        <v>1.2E-2</v>
+      </c>
+      <c r="H69" s="13">
+        <f t="shared" si="23"/>
+        <v>8.3999999999999991E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B70" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C70" s="2">
+        <f t="shared" si="21"/>
+        <v>0.3</v>
+      </c>
+      <c r="D70" s="2">
+        <f t="shared" si="22"/>
+        <v>0.7</v>
+      </c>
+      <c r="E70" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F70" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G70" s="13">
+        <f t="shared" si="20"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H70" s="13">
+        <f t="shared" si="23"/>
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B71" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C71" s="2">
+        <f t="shared" si="21"/>
+        <v>0.3</v>
+      </c>
+      <c r="D71" s="2">
+        <f t="shared" si="22"/>
+        <v>0.7</v>
+      </c>
+      <c r="E71" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F71" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="G71" s="13">
+        <f t="shared" ref="G71" si="24">B71*C71*E71</f>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H71" s="13">
+        <f>B71*D71*F71</f>
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G72" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F73" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G73" s="18">
+        <f>SUM(G66:G71)</f>
+        <v>7.3499999999999996E-2</v>
+      </c>
+      <c r="H73" s="18">
+        <f>SUM(H66:H71)</f>
+        <v>0.51449999999999996</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -2074,7 +2074,7 @@
         <v>0.05</v>
       </c>
       <c r="F33" s="16">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G33" s="13">
         <f t="shared" si="7"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H33" s="13">
         <f t="shared" si="9"/>
-        <v>3.4999999999999996E-2</v>
+        <v>2.6249999999999999E-2</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H39" s="19">
         <f>SUM(H29:H37)</f>
-        <v>0.749</v>
+        <v>0.74024999999999996</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -2310,7 +2310,7 @@
         <v>0.3</v>
       </c>
       <c r="D43" s="2">
-        <f t="shared" ref="D43:D50" si="12">L$2</f>
+        <f t="shared" ref="D43:D49" si="12">L$2</f>
         <v>0.7</v>
       </c>
       <c r="E43" s="16">
@@ -2497,7 +2497,7 @@
         <v>0.05</v>
       </c>
       <c r="F49" s="16">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G49" s="13">
         <f t="shared" si="10"/>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H49" s="13">
         <f t="shared" si="13"/>
-        <v>5.5999999999999994E-2</v>
+        <v>4.1999999999999996E-2</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H52" s="18">
         <f>SUM(H42:H50)</f>
-        <v>0.79099999999999993</v>
+        <v>0.77699999999999991</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -2738,18 +2738,18 @@
         <v>0.7</v>
       </c>
       <c r="E59" s="16">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F59" s="16">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="G59" s="13">
         <f t="shared" si="14"/>
-        <v>1.7999999999999999E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="H59" s="13">
         <f t="shared" si="17"/>
-        <v>0.126</v>
+        <v>6.3E-2</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -2826,11 +2826,11 @@
       </c>
       <c r="G63" s="18">
         <f>SUM(G55:G61)</f>
-        <v>9.2999999999999999E-2</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="H63" s="18">
         <f>SUM(H55:H61)</f>
-        <v>0.65100000000000002</v>
+        <v>0.58800000000000008</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">

--- a/clustering/sepsectors/VDS factors for each sector.xlsx
+++ b/clustering/sepsectors/VDS factors for each sector.xlsx
@@ -85,9 +85,6 @@
     <t>Распознование</t>
   </si>
   <si>
-    <t>30-90% (+ бесконечность)</t>
-  </si>
-  <si>
     <t>Оптимизация производства (брак, оборудование)</t>
   </si>
   <si>
@@ -377,6 +374,9 @@
   </si>
   <si>
     <t>Сектор J (Информация и связь)</t>
+  </si>
+  <si>
+    <t>50-90% (+ бесконечность)</t>
   </si>
 </sst>
 </file>
@@ -425,7 +425,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -468,6 +468,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -482,7 +488,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -535,6 +541,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -842,28 +854,28 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -874,25 +886,25 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -903,25 +915,25 @@
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -929,25 +941,25 @@
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -955,25 +967,25 @@
         <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -981,25 +993,25 @@
         <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1007,25 +1019,25 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1033,25 +1045,25 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1059,25 +1071,25 @@
         <v>9</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1085,16 +1097,16 @@
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1102,27 +1114,27 @@
         <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1146,7 +1158,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1170,12 +1182,12 @@
         <v>20</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>18</v>
@@ -1183,26 +1195,26 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1225,40 +1237,40 @@
     <col min="7" max="7" width="12.85546875" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="11" max="11" width="22.28515625" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="K1" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="20" t="s">
         <v>109</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -1291,10 +1303,10 @@
         <v>8.3999999999999991E-2</v>
       </c>
       <c r="J2" s="2"/>
-      <c r="K2" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="L2" s="2">
+      <c r="K2" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="L2" s="21">
         <v>0.7</v>
       </c>
       <c r="N2" s="2"/>
@@ -1540,17 +1552,17 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F11" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G11" s="18">
         <f>SUM(G2:G9)</f>
@@ -1563,33 +1575,33 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E13" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2">
         <v>0.6</v>
@@ -1619,7 +1631,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2">
         <v>0.4</v>
@@ -1649,7 +1661,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2">
         <v>0.4</v>
@@ -1679,7 +1691,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="2">
         <v>0.2</v>
@@ -1709,7 +1721,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2">
         <v>0.2</v>
@@ -1739,7 +1751,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2">
         <v>0.2</v>
@@ -1769,7 +1781,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2">
         <v>0.3</v>
@@ -1799,7 +1811,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2">
         <v>0.5</v>
@@ -1829,7 +1841,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" s="2">
         <v>0.25</v>
@@ -1859,7 +1871,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2">
         <v>0.2</v>
@@ -1889,16 +1901,16 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E25" s="1"/>
       <c r="F25" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G25" s="18">
         <f>SUM(G14:G23)</f>
@@ -1911,33 +1923,33 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H28" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="16">
         <v>0.4</v>
@@ -1967,7 +1979,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="16">
         <v>0.25</v>
@@ -1997,7 +2009,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" s="16">
         <v>0.3</v>
@@ -2027,7 +2039,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" s="16">
         <v>0.9</v>
@@ -2057,7 +2069,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B33" s="16">
         <v>0.25</v>
@@ -2087,7 +2099,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" s="16">
         <v>0.4</v>
@@ -2117,7 +2129,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B35" s="16">
         <v>0.3</v>
@@ -2147,7 +2159,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B36" s="16">
         <v>0.25</v>
@@ -2177,7 +2189,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" s="16">
         <v>0.2</v>
@@ -2211,10 +2223,10 @@
       <c r="D38" s="15"/>
       <c r="E38" s="15"/>
       <c r="G38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -2224,7 +2236,7 @@
       <c r="D39" s="16"/>
       <c r="E39" s="17"/>
       <c r="F39" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G39" s="19">
         <f>SUM(G29:G37)</f>
@@ -2244,33 +2256,33 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H41" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B42" s="16">
         <v>0.5</v>
@@ -2300,7 +2312,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B43" s="16">
         <v>0.4</v>
@@ -2330,7 +2342,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B44" s="16">
         <v>0.3</v>
@@ -2360,7 +2372,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B45" s="16">
         <v>0.3</v>
@@ -2390,7 +2402,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B46" s="16">
         <v>0.5</v>
@@ -2420,7 +2432,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B47" s="16">
         <v>0.3</v>
@@ -2450,7 +2462,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B48" s="16">
         <v>0.3</v>
@@ -2480,7 +2492,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B49" s="16">
         <v>0.4</v>
@@ -2510,7 +2522,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B50" s="16">
         <v>0.3</v>
@@ -2545,10 +2557,10 @@
       <c r="D51" s="15"/>
       <c r="E51" s="15"/>
       <c r="G51" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -2558,7 +2570,7 @@
       <c r="D52" s="16"/>
       <c r="E52" s="17"/>
       <c r="F52" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G52" s="18">
         <f>SUM(G42:G50)</f>
@@ -2578,33 +2590,33 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E54" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H54" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B55" s="2">
         <v>0.4</v>
@@ -2634,7 +2646,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B56" s="2">
         <v>0.5</v>
@@ -2664,7 +2676,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B57" s="2">
         <v>0.4</v>
@@ -2694,7 +2706,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B58" s="2">
         <v>0.4</v>
@@ -2724,7 +2736,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B59" s="2">
         <v>0.6</v>
@@ -2754,7 +2766,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B60" s="2">
         <v>0.5</v>
@@ -2784,7 +2796,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B61" s="2">
         <v>0.3</v>
@@ -2814,15 +2826,15 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G62" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F63" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G63" s="18">
         <f>SUM(G55:G61)</f>
@@ -2835,33 +2847,33 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C65" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E65" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H65" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B66" s="2">
         <v>0.7</v>
@@ -2891,7 +2903,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B67" s="2">
         <v>0.25</v>
@@ -2921,7 +2933,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B68" s="2">
         <v>0.3</v>
@@ -2951,7 +2963,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B69" s="2">
         <v>0.4</v>
@@ -2981,7 +2993,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B70" s="2">
         <v>0.5</v>
@@ -3011,7 +3023,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B71" s="2">
         <v>0.3</v>
@@ -3041,15 +3053,15 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G72" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H72" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F73" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G73" s="18">
         <f>SUM(G66:G71)</f>
